--- a/docs/Asset_Bible.xlsx
+++ b/docs/Asset_Bible.xlsx
@@ -10,6 +10,7 @@
     <sheet name="READ ME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="DASHBOARD" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="AFFINITY PIPELINE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPRITE SCALE" sheetId="5" state="visible" r:id="rId8"/>
     <sheet name="ASSETS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
@@ -323,7 +324,7 @@
     <t xml:space="preserve">Character sprite frame</t>
   </si>
   <si>
-    <t xml:space="preserve">32 x 48 px · 72 DPI · RGB/8 · transparent background. Sheet = 4 columns x 4 rows -&gt; canvas 128 x 192 px.</t>
+    <t xml:space="preserve">48 x 72 px · 72 DPI · RGB/8 · transparent. Sheet = 4 cols x 4 rows = 192 x 288 px. Feet on the frame's bottom edge. Character height varies by race (see SPRITE SCALE sheet) — Elorin/elves/humans 64 px, orcs 68-70 px, Terran 52 px, children 44 px.</t>
   </si>
   <si>
     <t xml:space="preserve">Tileset working canvas</t>
@@ -434,7 +435,7 @@
     <t xml:space="preserve">Step 3 — downscale with Nearest Neighbour</t>
   </si>
   <si>
-    <t xml:space="preserve">Document menu &gt; Resize Document. Set target size (e.g. 32 x 48). Set Resampling = NEAREST NEIGHBOUR. Never Bilinear/Bicubic/Lanczos — those blur. NOTE: in the unified app the resize options are still under Document while in Pixel studio, but sit deeper in the menu than they did in v2 — hunt for them once, then remember.</t>
+    <t xml:space="preserve">Document menu &gt; Resize Document. Set target size (e.g. 48 x 72). Set Resampling = NEAREST NEIGHBOUR. Never Bilinear/Bicubic/Lanczos — those blur. NOTE: in the unified app the resize options are still under Document while in Pixel studio, but sit deeper in the menu than they did in v2 — hunt for them once, then remember.</t>
   </si>
   <si>
     <t xml:space="preserve">Step 3b — ignore 'Pixel Art' resize</t>
@@ -446,7 +447,7 @@
     <t xml:space="preserve">Step 4 — the actual cleanup (the real work)</t>
   </si>
   <si>
-    <t xml:space="preserve">At 32x48 the downscale will be a mess. Zoom to 800-1600%, and with the Pixel Tool redraw: fix the silhouette first (it must read instantly at native size), then flatten stray in-between colours onto palette colours, then clean the outline to a single consistent pixel run. Budget 20-45 min per sprite. This is normal and unavoidable.</t>
+    <t xml:space="preserve">At 48x72 the downscale will be a mess. Zoom to 800-1600%, and with the Pixel Tool redraw: fix the silhouette first (it must read instantly at native size), then flatten stray in-between colours onto palette colours, then clean the outline to a single consistent pixel run. Budget 20-45 min per sprite. This is normal and unavoidable.</t>
   </si>
   <si>
     <t xml:space="preserve">Step 5 — check at native size</t>
@@ -494,7 +495,7 @@
     <t>Layout</t>
   </si>
   <si>
-    <t xml:space="preserve">One canvas, 128 x 192 px, grid on. Each 32x48 cell = one frame. Row 1 = walk down, row 2 = up, row 3 = left, row 4 = right.</t>
+    <t xml:space="preserve">One canvas, 192 x 288 px. Each 48x72 cell = one frame. Row 1 = walk down, row 2 = up, row 3 = left, row 4 = right.</t>
   </si>
   <si>
     <t xml:space="preserve">Build method</t>
@@ -578,13 +579,13 @@
     <t xml:space="preserve">P1 all acts</t>
   </si>
   <si>
-    <t xml:space="preserve">32x48/frame, 4-dir sheet</t>
+    <t xml:space="preserve">48x72/frame · 192x288 sheet (4x4)</t>
   </si>
   <si>
     <t xml:space="preserve">3 class palette variants (Voidweaver indigo-black / Harmonist silver-blue / Mender pale green)</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A Noctari night elf woman, mid-life scholar-archmage: long dark hair, elegant layered academy robes with subtle void-black trim, calm intense bearing. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A Noctari night elf woman, mid-life scholar-archmage: long dark hair, elegant layered academy robes with subtle void-black trim, calm intense bearing. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>2026-07-12</t>
@@ -605,7 +606,7 @@
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Same Noctari woman as CH-001 but in a hooded weathered travel cloak, worn satchel, wearier posture. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Same Noctari woman as CH-001 but in a hooded weathered travel cloak, worn satchel, wearier posture. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t xml:space="preserve">Use CH-001 output as reference image for consistency.</t>
@@ -620,7 +621,7 @@
     <t xml:space="preserve">P2 Act I</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A young orc labor-slave: lean but broad, ragged work clothes, iron collar, watchful intelligent eyes. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A young orc labor-slave: lean but broad, ragged work clothes, iron collar, watchful intelligent eyes. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-004</t>
@@ -635,7 +636,7 @@
     <t xml:space="preserve">Variant: archive disguise robes</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. The same orc in his prime: massive, scarred, controlled, plain laborer garb concealing discipline. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. The same orc in his prime: massive, scarred, controlled, plain laborer garb concealing discipline. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t xml:space="preserve">Reference CH-003 output for facial continuity.</t>
@@ -650,7 +651,7 @@
     <t xml:space="preserve">P2 Act III</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. The same orc as a scarred elder revolutionary: grey-streaked, upright, terrible resolve, dark leathers. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. The same orc as a scarred elder revolutionary: grey-streaked, upright, terrible resolve, dark leathers. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-006</t>
@@ -662,7 +663,7 @@
     <t xml:space="preserve">Cold Open, P1</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A young-looking elf apprentice scribe (~80, youthful for an elf): ink-stained fingers, satchel of scrolls, modest grey-blue robes. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A young-looking elf apprentice scribe (~80, youthful for an elf): ink-stained fingers, satchel of scrolls, modest grey-blue robes. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-007</t>
@@ -674,7 +675,7 @@
     <t xml:space="preserve">Cold Open, Coda</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. The same elf scribe aged and hollowed by catastrophe: dishevelled robes, clutching a chronicle ledger, haunted but resolute. Muted grey-violet palette. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. The same elf scribe aged and hollowed by catastrophe: dishevelled robes, clutching a chronicle ledger, haunted but resolute. Muted grey-violet palette. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-008</t>
@@ -686,7 +687,7 @@
     <t>P1</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A Solari sun elf woman, precise and immaculate: structured gold-white work robes, tool sash of enchanting instruments. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A Solari sun elf woman, precise and immaculate: structured gold-white work robes, tool sash of enchanting instruments. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-009</t>
@@ -695,7 +696,7 @@
     <t xml:space="preserve">Coil (Noctari theorist)</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A wiry Noctari man, Elorin's former student: rumpled scholar robes, spectacles, armful of notes, nervous energy. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A wiry Noctari man, Elorin's former student: rumpled scholar robes, spectacles, armful of notes, nervous energy. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-010</t>
@@ -704,7 +705,7 @@
     <t xml:space="preserve">Vara (human prodigy)</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A young human woman prodigy among elves: simple practical clothes, bright alert posture, slightly out of place. Warm earth-tone palette against elven surroundings. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A young human woman prodigy among elves: simple practical clothes, bright alert posture, slightly out of place. Warm earth-tone palette against elven surroundings. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-011</t>
@@ -713,7 +714,7 @@
     <t xml:space="preserve">Durak Ironthought (Terran geomancer)</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A stout Terran (dwarf-like earthfolk) geomancer: stone-grey skin, braided beard with copper rings, heavy tool harness, rune-etched chisels. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A stout Terran (dwarf-like earthfolk) geomancer: stone-grey skin, braided beard with copper rings, heavy tool harness, rune-etched chisels. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-012</t>
@@ -725,7 +726,7 @@
     <t xml:space="preserve">P1 memory scenes</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. An elderly Noctari mentor: serene, water-smooth robes in fading blues, walking staff, gentle gravity. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. An elderly Noctari mentor: serene, water-smooth robes in fading blues, walking staff, gentle gravity. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-013</t>
@@ -734,7 +735,7 @@
     <t xml:space="preserve">Corel (containment archmagister)</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. An exhausted Noctari archmagister: formal high-collared robes gone slightly unkempt, dark-ringed eyes, burden visible in the shoulders. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. An exhausted Noctari archmagister: formal high-collared robes gone slightly unkempt, dark-ringed eyes, burden visible in the shoulders. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-014</t>
@@ -746,7 +747,7 @@
     <t xml:space="preserve">2 color variants</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A haughty elven Conclave official: ceremonial layered robes, chain of office, imperious bearing. Mixed Noctari/Solari court palette. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A haughty elven Conclave official: ceremonial layered robes, chain of office, imperious bearing. Mixed Noctari/Solari court palette. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-015</t>
@@ -758,7 +759,7 @@
     <t xml:space="preserve">3 body/hair variants</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Young elven academy students in matching study robes with house-color sashes. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Young elven academy students in matching study robes with house-color sashes. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t xml:space="preserve">Crowd filler for Starfall.</t>
@@ -773,7 +774,7 @@
     <t xml:space="preserve">2 variants</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Mid-rank elven researcher: work robes with protective apron, glyph-marked gloves. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Mid-rank elven researcher: work robes with protective apron, glyph-marked gloves. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-017</t>
@@ -785,7 +786,7 @@
     <t xml:space="preserve">P1 Act III, P2 Act III</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. An elite vault guardian in sealed dark plate armor chased with silver null-glyphs, faceless helm, halberd of black glass. Intimidating silhouette. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. An elite vault guardian in sealed dark plate armor chased with silver null-glyphs, faceless helm, halberd of black glass. Intimidating silhouette. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t xml:space="preserve">Appears in BOTH parts - the vault's constant.</t>
@@ -800,7 +801,7 @@
     <t xml:space="preserve">4 variants (mixed ages)</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Ordinary Noctari city folk: merchants, lamplighters, parents, elders. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Ordinary Noctari city folk: merchants, lamplighters, parents, elders. Noctari (night elf) palette: deep indigo, violet, silver starlight accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-019</t>
@@ -812,7 +813,7 @@
     <t>P2</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. An orc woman elder, the revolution's conscience: iron-grey braids, patched war-coat, carries herself like a judge. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. An orc woman elder, the revolution's conscience: iron-grey braids, patched war-coat, carries herself like a judge. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-020</t>
@@ -821,7 +822,7 @@
     <t>Kess</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A young orc courier/agent: quick, slight for an orc, hooded wrap, message tubes at the belt. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A young orc courier/agent: quick, slight for an orc, hooded wrap, message tubes at the belt. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-021</t>
@@ -833,7 +834,7 @@
     <t xml:space="preserve">3 variants</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Enslaved orc laborers: iron collars, tool harnesses, ash-dusted work clothes, weary strength. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Enslaved orc laborers: iron collars, tool harnesses, ash-dusted work clothes, weary strength. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-022</t>
@@ -845,7 +846,7 @@
     <t xml:space="preserve">P2 Act I (Black Crag)</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Orc rebellion fighter: improvised armor from labor gear, broken-chain motif painted on chest. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Orc rebellion fighter: improvised armor from labor gear, broken-chain motif painted on chest. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-023</t>
@@ -854,7 +855,7 @@
     <t xml:space="preserve">Elven overseer</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. A cold elven labor overseer: crisp uniform coat, glyph-tipped rod of office, contemptuous posture. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. A cold elven labor overseer: crisp uniform coat, glyph-tipped rod of office, contemptuous posture. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-024</t>
@@ -863,7 +864,7 @@
     <t xml:space="preserve">Facility researcher (Solari)</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Solari facility researcher: pristine work robes, clipboard scroll-frame, oblivious to the labor around them. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Solari facility researcher: pristine work robes, clipboard scroll-frame, oblivious to the labor around them. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-025</t>
@@ -872,7 +873,7 @@
     <t xml:space="preserve">Archivist of Astral Wisdom</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. An ancient elven archivist: dust-colored robes, key-ring of dozens of archive keys, lantern-staff. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. An ancient elven archivist: dust-colored robes, key-ring of dozens of archive keys, lantern-staff. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-026</t>
@@ -881,7 +882,7 @@
     <t xml:space="preserve">Solari Tower guard</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Tower of Celestial Harmony guard: gilded ceremonial half-plate, sun-disc shield, spear. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Tower of Celestial Harmony guard: gilded ceremonial half-plate, sun-disc shield, spear. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t xml:space="preserve">Shared across both parts - build once.</t>
@@ -893,7 +894,7 @@
     <t xml:space="preserve">Astra'Thalas citizen set</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Solari capital citizens in festival dress for the solstice. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Solari capital citizens in festival dress for the solstice. Solari (sun elf) palette: radiant gold, ivory, white marble, dawn-orange accents. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>CH-028</t>
@@ -902,7 +903,7 @@
     <t xml:space="preserve">Ashpile child</t>
   </si>
   <si>
-    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 32x48 px per frame). Grid layout: 4 rows = walk down / up / left / right, 4 frames per row, plus one idle frame per direction at row end. Orc children of the birth-camp: small, quick, ragged, resilient. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
+    <t xml:space="preserve">HD pixel art character sprite sheet for a top-down 2D dark-fantasy RPG (Zelda: Minish Cap fidelity, 48x72 px per frame). Grid layout: 4 rows = walk down / up / left / right, exactly 4 frames per row (walk cycle: contact-pass-contact-pass), 4 rows only, no extra columns. Orc children of the birth-camp: small, quick, ragged, resilient. orc/Ashpile palette: ash grey, iron, rust, ember orange. Clean readable silhouette, crisp pixel clusters, no anti-aliasing, unified palette, flat solid magenta background for easy removal.</t>
   </si>
   <si>
     <t>PO-001</t>
@@ -7933,8 +7934,61 @@
         <v>649</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EN-019</t>
+        </is>
+      </c>
+      <c r="B131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Environment</t>
+        </is>
+      </c>
+      <c r="C131" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Astra'Thalas - the scriptorium (Cold Open)</t>
+        </is>
+      </c>
+      <c r="D131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cold Open</t>
+        </is>
+      </c>
+      <c r="E131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 - Vertical Slice</t>
+        </is>
+      </c>
+      <c r="F131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32x32 tiles + props</t>
+        </is>
+      </c>
+      <c r="G131" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Floor, wall, window, desk, cold cup. Lit and unlit states for the Silence.</t>
+        </is>
+      </c>
+      <c r="H131" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HD pixel art top-down interior for a dark-fantasy RPG. The record scriptorium of an elven astral archive at night, directly below a festival balcony. Ranked scroll racks along the back wall, reading desks, a tall window showing the lit festival city beyond, an indigo lacquered locked cabinet. Cold, orderly, deserted - everyone has gone to the festival. Lit only by a reading lamp and the gold spill through the window. Muted Noctari indigo, grey stone, parchment, aged wood. 32x32 tile grid.</t>
+        </is>
+      </c>
+      <c r="I131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placeholder</t>
+        </is>
+      </c>
+      <c r="J131" s="25"/>
+      <c r="K131" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW 2026-07-17. The room below the Cold Open stair. EN-017/018 were already claimed by the Starfall and Umbraveil map prompts, so this took the next free id. Currently a labelled placeholder in godot/art/placeholders/EN-019_*.png.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K130">
+  <autoFilter ref="A1:K131">
     <filterColumn colId="4">
       <filters>
         <filter val="P1 - Vertical Slice"/>
@@ -7960,7 +8014,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:I130</xm:sqref>
+          <xm:sqref>I2:I131</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="3" aboveAverage="0" operator="equal" rank="0" text="" id="{64BA7576-03C8-4468-B7DB-7F604EEAF2B9}">
@@ -7974,7 +8028,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:I130</xm:sqref>
+          <xm:sqref>I2:I131</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="4" aboveAverage="0" operator="equal" rank="0" text="" id="{4EB68374-0C63-4035-B173-74A8929354FD}">
@@ -7988,7 +8042,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:I130</xm:sqref>
+          <xm:sqref>I2:I131</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="5" aboveAverage="0" operator="equal" rank="0" text="" id="{B161561E-003D-47ED-AA51-6F5A44D0A598}">
@@ -8002,7 +8056,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:I130</xm:sqref>
+          <xm:sqref>I2:I131</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="6" aboveAverage="0" operator="equal" rank="0" text="" id="{39A8F38E-0B32-4D29-837A-EE694859844C}">
@@ -8016,7 +8070,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:I130</xm:sqref>
+          <xm:sqref>I2:I131</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="7" aboveAverage="0" operator="equal" rank="0" text="" id="{714DF619-7F70-48D2-996C-A881270942CF}">
@@ -8030,7 +8084,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:I130</xm:sqref>
+          <xm:sqref>I2:I131</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -8043,10 +8097,258 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>I2:I130</xm:sqref>
+          <xm:sqref>I2:I131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="82" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Character group</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Height in frame</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Children</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~44 px</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CH-028</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terran (Durak)</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~52 px (broad)</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CH-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elves &amp; humans</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~62-64 px</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CH-001/002, CH-006-010, CH-012-018, CH-023-027</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Void Wardens (armoured)</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~68 px</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CH-017</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orcs</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~68-70 px</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CH-003/004/005, CH-019-022, CH-028 (adult)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRAME SPEC (locked 2026-07-17)</t>
+        </is>
+      </c>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprite frame</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48 x 72 px</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48 px width confirmed sufficient by the user, 2026-07-17.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprite sheet</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192 x 288 px</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 columns x 4 rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Row order</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0=down 1=up 2=left 3=right</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lock this. Godot slices SpriteFrames in this order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baseline</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feet on the frame's bottom edge</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headroom varies; the feet do not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tile grid</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32 x 32 px</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tilesets ONLY. Nothing to do with sprite frames.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REFERENCE</t>
+        </is>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CH-001 (Elorin)</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64 px tall in a 48x72 frame</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Already produced. Every other elf/human matches her. Do not re-derive this from anything else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Native viewport is 960 x 540 (GDD S13).</t>
+        </is>
+      </c>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Never judge sprite size in Affinity at 100%. The only honest size check is running the sheet in Godot.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/docs/Asset_Bible.xlsx
+++ b/docs/Asset_Bible.xlsx
@@ -8267,12 +8267,12 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0=down 1=up 2=left 3=right</t>
+          <t xml:space="preserve">0=down 1=up 2=right 3=left</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lock this. Godot slices SpriteFrames in this order.</t>
+          <t xml:space="preserve">Lock this. Confirmed against the cleaned CH-001 sheet 2026-07-17 - the art is the ground truth here, not the other way round.</t>
         </is>
       </c>
     </row>
